--- a/data/trans_orig/P35A_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P35A_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su médico le ha aconsejado que siga una alimentación saludable en 2023</t>
+          <t>Población según si su médico le ha aconsejado que siga una alimentación saludable en 2023 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27109</t>
+          <t>26841</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>71041</t>
+          <t>69994</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19944</t>
+          <t>20633</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51254</t>
+          <t>49023</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>54115</t>
+          <t>55756</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>101692</t>
+          <t>102112</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,32%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2919</t>
+          <t>2757</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22164</t>
+          <t>22851</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1206</t>
+          <t>1587</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12387</t>
+          <t>12454</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6296</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28421</t>
+          <t>28867</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11476</t>
+          <t>10985</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>50646</t>
+          <t>50658</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24422</t>
+          <t>22900</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>55664</t>
+          <t>56274</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>43243</t>
+          <t>42122</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>92188</t>
+          <t>94040</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,19%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>291232</t>
+          <t>288178</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>346552</t>
+          <t>345593</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>216654</t>
+          <t>216823</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>256743</t>
+          <t>259247</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>69,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>528433</t>
+          <t>524088</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>591364</t>
+          <t>591451</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,93%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19780</t>
+          <t>20945</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>46433</t>
+          <t>47481</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18687</t>
+          <t>18285</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>45124</t>
+          <t>45019</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>45957</t>
+          <t>45551</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>82767</t>
+          <t>83594</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,94%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9029</t>
+          <t>9093</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26394</t>
+          <t>25586</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5647</t>
+          <t>5662</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19623</t>
+          <t>21495</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17345</t>
+          <t>17335</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39986</t>
+          <t>40061</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35477</t>
+          <t>35914</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>72846</t>
+          <t>70658</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>44510</t>
+          <t>40824</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>86951</t>
+          <t>87563</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>87699</t>
+          <t>88731</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>146878</t>
+          <t>146247</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,64%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>302234</t>
+          <t>299546</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>345772</t>
+          <t>343678</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>374093</t>
+          <t>374998</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>441057</t>
+          <t>444559</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>691864</t>
+          <t>692457</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>773644</t>
+          <t>775152</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>82,9%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>31399</t>
+          <t>31371</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>58393</t>
+          <t>58245</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>29958</t>
+          <t>30797</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>49945</t>
+          <t>50457</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>66938</t>
+          <t>67279</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>99113</t>
+          <t>100207</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,29%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6959</t>
+          <t>7345</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21846</t>
+          <t>20994</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13604</t>
+          <t>14452</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>28764</t>
+          <t>29057</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>24745</t>
+          <t>24670</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>44610</t>
+          <t>44263</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>70397</t>
+          <t>69707</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>104422</t>
+          <t>105510</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>86901</t>
+          <t>86298</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>117590</t>
+          <t>116204</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>165485</t>
+          <t>165215</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>209003</t>
+          <t>210810</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,54%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>373365</t>
+          <t>372983</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>415190</t>
+          <t>415015</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>361755</t>
+          <t>362575</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>397595</t>
+          <t>399215</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>747359</t>
+          <t>743982</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>801097</t>
+          <t>798207</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>68,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>73,99%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16586</t>
+          <t>17064</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>64558</t>
+          <t>64569</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30528</t>
+          <t>29369</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>51750</t>
+          <t>49461</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>46810</t>
+          <t>49556</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>101560</t>
+          <t>105142</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4991</t>
+          <t>5046</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>25526</t>
+          <t>24992</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>16335</t>
+          <t>15879</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>31371</t>
+          <t>31806</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>22300</t>
+          <t>22170</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>51852</t>
+          <t>52230</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>218427</t>
+          <t>217855</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>673455</t>
+          <t>684230</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>145320</t>
+          <t>141444</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>193484</t>
+          <t>194772</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>383375</t>
+          <t>385650</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>985963</t>
+          <t>935760</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>58,47%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>189970</t>
+          <t>185193</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>592530</t>
+          <t>596179</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>454055</t>
+          <t>454314</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>512835</t>
+          <t>519012</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>539866</t>
+          <t>580000</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1077527</t>
+          <t>1074686</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>67,16%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>35012</t>
+          <t>35261</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>60653</t>
+          <t>60022</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>24207</t>
+          <t>24176</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>40739</t>
+          <t>40396</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>65266</t>
+          <t>64695</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>95282</t>
+          <t>95229</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10995</t>
+          <t>10818</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>24667</t>
+          <t>24384</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15125</t>
+          <t>15544</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>29009</t>
+          <t>28811</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>29628</t>
+          <t>28715</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>49960</t>
+          <t>48179</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>166660</t>
+          <t>164073</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>210875</t>
+          <t>206640</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>146428</t>
+          <t>144234</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>179168</t>
+          <t>176829</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>320556</t>
+          <t>323358</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>374651</t>
+          <t>374775</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,79%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>285575</t>
+          <t>288515</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>333976</t>
+          <t>332897</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>314902</t>
+          <t>315899</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>349542</t>
+          <t>349731</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>616554</t>
+          <t>615958</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>672054</t>
+          <t>672564</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,53%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,64%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>23099</t>
+          <t>22935</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>40747</t>
+          <t>40087</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>10015</t>
+          <t>12283</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>43523</t>
+          <t>44057</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>32063</t>
+          <t>30145</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>78509</t>
+          <t>79307</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>7281</t>
+          <t>7470</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>18876</t>
+          <t>18545</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3079</t>
+          <t>2824</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>16862</t>
+          <t>17304</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>11217</t>
+          <t>11194</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>32648</t>
+          <t>32143</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>125801</t>
+          <t>127385</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>156554</t>
+          <t>156153</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>62833</t>
+          <t>68573</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>231294</t>
+          <t>232650</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>158330</t>
+          <t>153872</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>377514</t>
+          <t>378605</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,77%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>168548</t>
+          <t>168496</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>198671</t>
+          <t>198244</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>53,85%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>321274</t>
+          <t>320816</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>531770</t>
+          <t>524097</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>52,73%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>497358</t>
+          <t>497174</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>771297</t>
+          <t>777348</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>50,91%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>79,6%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>15088</t>
+          <t>14602</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>29427</t>
+          <t>29259</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>21750</t>
+          <t>21142</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>36568</t>
+          <t>36192</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>40641</t>
+          <t>39522</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>60944</t>
+          <t>59990</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3144</t>
+          <t>2924</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>10844</t>
+          <t>10507</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>6134</t>
+          <t>5432</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>14925</t>
+          <t>14406</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>10939</t>
+          <t>10991</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>22192</t>
+          <t>22318</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>109673</t>
+          <t>109138</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>134844</t>
+          <t>135771</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>162963</t>
+          <t>162513</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>191624</t>
+          <t>193381</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>278955</t>
+          <t>280565</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>317453</t>
+          <t>320245</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>45,26%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>120139</t>
+          <t>120468</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>146744</t>
+          <t>146507</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>51,81%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>194465</t>
+          <t>193729</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>224258</t>
+          <t>225379</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>324510</t>
+          <t>321879</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>363748</t>
+          <t>362205</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,19%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>203570</t>
+          <t>201115</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>299651</t>
+          <t>299922</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>187843</t>
+          <t>188587</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>261118</t>
+          <t>263072</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>429352</t>
+          <t>423486</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>542449</t>
+          <t>545458</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>65449</t>
+          <t>64626</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>107807</t>
+          <t>108413</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>79958</t>
+          <t>77182</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>119839</t>
+          <t>118295</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>158291</t>
+          <t>155921</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>218508</t>
+          <t>215692</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>821124</t>
+          <t>818537</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>1538492</t>
+          <t>1552499</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>679621</t>
+          <t>703501</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>939244</t>
+          <t>950087</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1657581</t>
+          <t>1654042</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>2547449</t>
+          <t>2478535</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>34,81%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1659202</t>
+          <t>1639125</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2273100</t>
+          <t>2275089</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2366842</t>
+          <t>2358953</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2703283</t>
+          <t>2699288</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>4068758</t>
+          <t>4031073</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>4795479</t>
+          <t>4786999</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>67,23%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P35A_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P35A_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>43953</t>
+          <t>47741</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26841</t>
+          <t>28650</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69994</t>
+          <t>70265</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>31912</t>
+          <t>41230</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20633</t>
+          <t>26699</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49023</t>
+          <t>60289</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>75864</t>
+          <t>88971</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55756</t>
+          <t>64621</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>102112</t>
+          <t>119716</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>15,54%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8572</t>
+          <t>8788</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2757</t>
+          <t>2504</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22851</t>
+          <t>22045</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>5598</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1587</t>
+          <t>1530</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12454</t>
+          <t>14138</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>13645</t>
+          <t>14386</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>6226</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28867</t>
+          <t>28067</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>25857</t>
+          <t>23931</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10985</t>
+          <t>11844</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>50658</t>
+          <t>45079</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>37469</t>
+          <t>42694</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22900</t>
+          <t>28185</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>56274</t>
+          <t>64861</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>63326</t>
+          <t>66625</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>42122</t>
+          <t>45217</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>94040</t>
+          <t>93059</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>12,08%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>321605</t>
+          <t>327333</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>288178</t>
+          <t>297659</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>345593</t>
+          <t>350026</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>238747</t>
+          <t>272990</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>216823</t>
+          <t>248543</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>259247</t>
+          <t>293490</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>560352</t>
+          <t>600323</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>524088</t>
+          <t>563851</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>591451</t>
+          <t>632769</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>82,15%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31338</t>
+          <t>38950</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20945</t>
+          <t>27010</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>47481</t>
+          <t>56868</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>31510</t>
+          <t>39343</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18285</t>
+          <t>28279</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>45019</t>
+          <t>53602</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>62848</t>
+          <t>78292</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>45551</t>
+          <t>60314</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>83594</t>
+          <t>100919</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>10,32%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15438</t>
+          <t>18105</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9093</t>
+          <t>9930</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25586</t>
+          <t>30140</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,67 +1442,67 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>11456</t>
+          <t>14084</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5662</t>
+          <t>7986</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21495</t>
+          <t>23495</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
+          <t>2,81%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>4,69%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>32189</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>21916</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>46174</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>3,29%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>2,24%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>4,2%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>26894</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>17335</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>40061</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>2,88%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>1,85%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>51610</t>
+          <t>59412</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35914</t>
+          <t>41436</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>70658</t>
+          <t>81384</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>66648</t>
+          <t>72944</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>40824</t>
+          <t>57808</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>87563</t>
+          <t>91971</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>118258</t>
+          <t>132356</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>88731</t>
+          <t>108819</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>146247</t>
+          <t>160056</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>16,37%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>325161</t>
+          <t>360424</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>299546</t>
+          <t>334133</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>343678</t>
+          <t>383352</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>401890</t>
+          <t>374712</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>374998</t>
+          <t>353411</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>444559</t>
+          <t>394554</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>727051</t>
+          <t>735136</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>692457</t>
+          <t>702582</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>775152</t>
+          <t>764455</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>78,17%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>42962</t>
+          <t>50860</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>31371</t>
+          <t>37471</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>58245</t>
+          <t>67318</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>39535</t>
+          <t>46911</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>30797</t>
+          <t>35884</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>50457</t>
+          <t>58617</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>82497</t>
+          <t>97771</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>67279</t>
+          <t>81265</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>100207</t>
+          <t>117761</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13148</t>
+          <t>15952</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7345</t>
+          <t>8734</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20994</t>
+          <t>24498</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20764</t>
+          <t>23745</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14452</t>
+          <t>16888</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29057</t>
+          <t>33477</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>33912</t>
+          <t>39697</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>24670</t>
+          <t>29337</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>44263</t>
+          <t>53080</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>86057</t>
+          <t>96663</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>69707</t>
+          <t>78982</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>105510</t>
+          <t>116689</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>100976</t>
+          <t>118079</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>86298</t>
+          <t>102692</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>116204</t>
+          <t>137884</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>187033</t>
+          <t>214742</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>165215</t>
+          <t>190996</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>210810</t>
+          <t>241854</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,46%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>394171</t>
+          <t>457362</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>372983</t>
+          <t>434690</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>415015</t>
+          <t>480928</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>381192</t>
+          <t>433404</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>362575</t>
+          <t>414642</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>399215</t>
+          <t>453225</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>775363</t>
+          <t>890767</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>743982</t>
+          <t>860583</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>798207</t>
+          <t>920277</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>74,04%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>41117</t>
+          <t>48446</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17064</t>
+          <t>36867</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>64569</t>
+          <t>64624</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>39595</t>
+          <t>44132</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>29369</t>
+          <t>34385</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49461</t>
+          <t>55476</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>80712</t>
+          <t>92578</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>49556</t>
+          <t>77139</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>105142</t>
+          <t>112370</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>14458</t>
+          <t>16252</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5046</t>
+          <t>8946</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>24992</t>
+          <t>25565</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>22812</t>
+          <t>25312</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15879</t>
+          <t>18178</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>31806</t>
+          <t>34101</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>37270</t>
+          <t>41564</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>22170</t>
+          <t>31788</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>52230</t>
+          <t>54637</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>409047</t>
+          <t>181877</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>217855</t>
+          <t>159670</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>684230</t>
+          <t>207110</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>172274</t>
+          <t>186089</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>141444</t>
+          <t>165597</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>194772</t>
+          <t>205508</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>581322</t>
+          <t>367966</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>385650</t>
+          <t>339007</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>935760</t>
+          <t>403115</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>28,05%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>423164</t>
+          <t>454041</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>185193</t>
+          <t>428748</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>596179</t>
+          <t>480405</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>64,81%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>477816</t>
+          <t>480963</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>454314</t>
+          <t>459729</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>519012</t>
+          <t>502348</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>68,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>900981</t>
+          <t>935004</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>580000</t>
+          <t>898235</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1074686</t>
+          <t>968877</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>65,06%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>67,42%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>47357</t>
+          <t>52796</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>35261</t>
+          <t>39991</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>60022</t>
+          <t>66998</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>31747</t>
+          <t>34977</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>24176</t>
+          <t>26370</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>40396</t>
+          <t>45609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>79104</t>
+          <t>87773</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>64695</t>
+          <t>72171</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>95229</t>
+          <t>105954</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>16638</t>
+          <t>19370</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10818</t>
+          <t>13042</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>24384</t>
+          <t>28400</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>21298</t>
+          <t>24063</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15544</t>
+          <t>17504</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>28811</t>
+          <t>33138</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>37936</t>
+          <t>43433</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>28715</t>
+          <t>33844</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>48179</t>
+          <t>56700</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>186676</t>
+          <t>198956</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>164073</t>
+          <t>177407</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>206640</t>
+          <t>224080</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>161624</t>
+          <t>183590</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>144234</t>
+          <t>165735</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>176829</t>
+          <t>201454</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,17 +3297,17 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>348299</t>
+          <t>382547</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>323358</t>
+          <t>353992</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>374775</t>
+          <t>408803</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>33,56%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>310564</t>
+          <t>338223</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>288515</t>
+          <t>314396</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>332897</t>
+          <t>362777</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>333236</t>
+          <t>366225</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>315899</t>
+          <t>345957</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>349731</t>
+          <t>384763</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>60,15%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>643800</t>
+          <t>704449</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>615958</t>
+          <t>676605</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>672564</t>
+          <t>733958</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>57,83%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>60,25%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>30765</t>
+          <t>35040</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>22935</t>
+          <t>25758</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>40087</t>
+          <t>46308</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>26804</t>
+          <t>29834</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>12283</t>
+          <t>22424</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>44057</t>
+          <t>38817</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>57569</t>
+          <t>64874</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>30145</t>
+          <t>52236</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>79307</t>
+          <t>77837</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -3683,17 +3683,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>11926</t>
+          <t>13191</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>7470</t>
+          <t>8359</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>18545</t>
+          <t>20506</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>9561</t>
+          <t>10685</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2824</t>
+          <t>6353</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>17304</t>
+          <t>16370</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>21487</t>
+          <t>23876</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>11194</t>
+          <t>16908</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>32143</t>
+          <t>32796</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>142377</t>
+          <t>154224</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>127385</t>
+          <t>137163</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>156153</t>
+          <t>170472</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>149443</t>
+          <t>164377</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>68573</t>
+          <t>149427</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>232650</t>
+          <t>179167</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>291820</t>
+          <t>318601</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>153872</t>
+          <t>295303</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>378605</t>
+          <t>341021</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>40,3%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>183097</t>
+          <t>204624</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>168496</t>
+          <t>187816</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>198244</t>
+          <t>221880</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>53,85%</t>
+          <t>54,51%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>422560</t>
+          <t>234270</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>320816</t>
+          <t>219320</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>524097</t>
+          <t>249456</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>605657</t>
+          <t>438894</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>497174</t>
+          <t>415929</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>777348</t>
+          <t>462652</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>54,67%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>21512</t>
+          <t>23787</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>14602</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>29259</t>
+          <t>32150</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>28085</t>
+          <t>30807</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>21142</t>
+          <t>23346</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>36192</t>
+          <t>39053</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>49597</t>
+          <t>54593</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>39522</t>
+          <t>43626</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>59990</t>
+          <t>66228</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>6910</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2924</t>
+          <t>3489</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>10507</t>
+          <t>12154</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,67 +4287,67 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>10827</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>5432</t>
+          <t>6790</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>14406</t>
+          <t>16627</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>3,59%</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>17738</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>12327</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>25644</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
           <t>2,29%</t>
         </is>
       </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>3,39%</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>15920</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>10991</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>22318</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>121613</t>
+          <t>131473</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>109138</t>
+          <t>116916</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>135771</t>
+          <t>146253</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>177305</t>
+          <t>194098</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>162513</t>
+          <t>178183</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>193381</t>
+          <t>210786</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>298918</t>
+          <t>325571</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>280565</t>
+          <t>302497</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>320245</t>
+          <t>347555</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>44,92%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>133437</t>
+          <t>148028</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>120468</t>
+          <t>132516</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>146507</t>
+          <t>163255</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>52,63%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>209748</t>
+          <t>227872</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>193729</t>
+          <t>210729</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>225379</t>
+          <t>244218</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>343185</t>
+          <t>375900</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>321879</t>
+          <t>353390</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>362205</t>
+          <t>399614</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>51,64%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>424861</t>
+          <t>463604</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>424861</t>
+          <t>463604</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>424861</t>
+          <t>463604</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>707620</t>
+          <t>773802</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>707620</t>
+          <t>773802</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>707620</t>
+          <t>773802</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>259003</t>
+          <t>297620</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>201115</t>
+          <t>260999</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>299922</t>
+          <t>336109</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>229188</t>
+          <t>267232</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>188587</t>
+          <t>238931</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>263072</t>
+          <t>301507</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>488192</t>
+          <t>564853</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>423486</t>
+          <t>519408</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>545458</t>
+          <t>613316</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,44%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>86377</t>
+          <t>98568</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>64626</t>
+          <t>78419</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>108413</t>
+          <t>120532</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>100687</t>
+          <t>114314</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>77182</t>
+          <t>97839</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>118295</t>
+          <t>134168</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>187064</t>
+          <t>212882</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>155921</t>
+          <t>186122</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>215692</t>
+          <t>239922</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>1023237</t>
+          <t>846536</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>818537</t>
+          <t>796297</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>1552499</t>
+          <t>906403</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>865740</t>
+          <t>961872</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>703501</t>
+          <t>917302</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>950087</t>
+          <t>1008674</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>1888977</t>
+          <t>1808408</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1654042</t>
+          <t>1736253</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>2478535</t>
+          <t>1882787</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>25,91%</t>
         </is>
       </c>
     </row>
@@ -5047,32 +5047,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>2091200</t>
+          <t>2290037</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1639125</t>
+          <t>2224767</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2275089</t>
+          <t>2348590</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5082,32 +5082,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2465189</t>
+          <t>2390437</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2358953</t>
+          <t>2335252</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2699288</t>
+          <t>2437888</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>62,54%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>4556388</t>
+          <t>4680474</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>4031073</t>
+          <t>4599983</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>4786999</t>
+          <t>4760746</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>64,41%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>65,52%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>3660804</t>
+          <t>3733855</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>3660804</t>
+          <t>3733855</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3660804</t>
+          <t>3733855</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>7120621</t>
+          <t>7266617</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>7120621</t>
+          <t>7266617</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>7120621</t>
+          <t>7266617</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
